--- a/database/controller_excel/Resguardo_Sandra_Castellanos.xlsx
+++ b/database/controller_excel/Resguardo_Sandra_Castellanos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Fecha:</t>
   </si>
   <si>
+    <t>29/04/2025</t>
+  </si>
+  <si>
     <t>Nombre:</t>
   </si>
   <si>
@@ -95,7 +98,7 @@
     <t>061W3CNJ802854B</t>
   </si>
   <si>
-    <t>tdfyopñlkjfigoñl</t>
+    <t>El equipo se reemplaza porque si</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -260,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
@@ -402,6 +405,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="true">
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -797,8 +804,8 @@
       <c r="H8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
-        <v>45770.0</v>
+      <c r="I8" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="15">
@@ -814,11 +821,11 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="15">
       <c r="A10" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -841,23 +848,23 @@
     <row r="12" spans="1:10" customHeight="1" ht="15">
       <c r="A12" s="2"/>
       <c r="B12" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="18"/>
     </row>
@@ -874,7 +881,7 @@
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="15">
       <c r="A14" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -920,49 +927,49 @@
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="15">
       <c r="A18" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="15">
-      <c r="A19" s="22">
+      <c r="A19" s="38">
         <v>1</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="B19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="C19" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22" t="s">
+      <c r="D19" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22" t="s">
+      <c r="E19" s="38"/>
+      <c r="F19" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="22"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
       <c r="A20" s="16"/>
@@ -988,7 +995,7 @@
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="26"/>
@@ -1012,7 +1019,7 @@
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -1025,7 +1032,7 @@
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
@@ -1038,7 +1045,7 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -1051,7 +1058,7 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="24.05">
       <c r="A27" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
@@ -1065,7 +1072,7 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27">
       <c r="A28" s="28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -1089,7 +1096,7 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="39">
       <c r="A30" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
@@ -1125,14 +1132,14 @@
     <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="32"/>
       <c r="B33" s="34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H33" s="35"/>
       <c r="I33" s="35"/>
@@ -1142,7 +1149,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -1175,7 +1182,7 @@
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="2"/>
       <c r="B37" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
@@ -1191,7 +1198,7 @@
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="2"/>
       <c r="B38" s="34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="34"/>
@@ -1277,7 +1284,7 @@
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/database/controller_excel/Resguardo_Sandra_Castellanos.xlsx
+++ b/database/controller_excel/Resguardo_Sandra_Castellanos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>29/04/2025</t>
+    <t>28/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>061W3CNJ802854B</t>
-  </si>
-  <si>
-    <t>El equipo se reemplaza porque si</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -966,9 +963,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
-        <v>26</v>
-      </c>
+      <c r="H19" s="38"/>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
@@ -995,7 +990,7 @@
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="26"/>
@@ -1019,7 +1014,7 @@
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -1032,7 +1027,7 @@
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
@@ -1045,7 +1040,7 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -1058,7 +1053,7 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="24.05">
       <c r="A27" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
@@ -1072,7 +1067,7 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27">
       <c r="A28" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -1096,7 +1091,7 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="39">
       <c r="A30" s="31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
@@ -1132,14 +1127,14 @@
     <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="32"/>
       <c r="B33" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H33" s="35"/>
       <c r="I33" s="35"/>
@@ -1149,7 +1144,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -1182,7 +1177,7 @@
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="2"/>
       <c r="B37" s="34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
@@ -1198,7 +1193,7 @@
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="2"/>
       <c r="B38" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="34"/>

--- a/database/controller_excel/Resguardo_Sandra_Castellanos.xlsx
+++ b/database/controller_excel/Resguardo_Sandra_Castellanos.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>28/04/2025</t>
+    <t>29/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
